--- a/AAII_Financials/Quarterly/PUBM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PUBM_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,289 +656,314 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>84600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>63700</v>
+      </c>
+      <c r="F8" s="3">
         <v>63300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>55400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>74300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>64500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>63000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>54600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>75600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>58100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>49700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>43600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>56200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>37800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>26400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>28300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>34400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>28500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>27400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>23600</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>26100</v>
+      </c>
+      <c r="F9" s="3">
         <v>25100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>23900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>23000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>21600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>19000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>18000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>16900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>16000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>13100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>12300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>11500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>10500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>9200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>10100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>9300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>9600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>8400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>8800</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>60400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>37600</v>
+      </c>
+      <c r="F10" s="3">
         <v>38200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>31500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>51300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>42900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>44000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>36600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>58700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>42100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>36600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>31300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>44800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>27300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>17200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>18200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>25100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>18900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>19000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>14800</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -961,70 +986,78 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E12" s="3">
+        <v>6600</v>
+      </c>
+      <c r="F12" s="3">
         <v>6700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>6500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>5900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>5100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>5100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>4800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>4100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>4100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>3900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>3700</v>
-      </c>
-      <c r="N12" s="3">
-        <v>3000</v>
-      </c>
-      <c r="O12" s="3">
-        <v>3400</v>
       </c>
       <c r="P12" s="3">
         <v>3000</v>
       </c>
       <c r="Q12" s="3">
+        <v>3400</v>
+      </c>
+      <c r="R12" s="3">
+        <v>3000</v>
+      </c>
+      <c r="S12" s="3">
         <v>2900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>3100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>3000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>3300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>3100</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,8 +1118,14 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1147,8 +1186,14 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1209,8 +1254,14 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1281,146 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>64200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>64200</v>
+      </c>
+      <c r="F17" s="3">
         <v>70500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>66100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>57800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>54900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>53200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>50000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>47600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>44000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>39500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>37000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>34000</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R17" s="3">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T17" s="3">
         <v>28500</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-7200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-10700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>16500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>9600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>9800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>4600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>28000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>14100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>10200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>6600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>22200</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3">
         <v>5900</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,132 +1443,146 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F20" s="3">
         <v>2000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-4900</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>1600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>5700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-500</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>13300</v>
+      </c>
+      <c r="F21" s="3">
         <v>5700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>2200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>27500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>13800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>17100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>13400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>40800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>20600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>15000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>11400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>25900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>18500</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1564,132 +1643,150 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-5200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-9200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>16800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>4700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>9700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>6200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>33700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>14300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>9900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>6800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>21700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>7900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>1300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>5800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>4000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>2200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-2800</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E24" s="3">
+        <v>100</v>
+      </c>
+      <c r="F24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-3400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>4000</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H24" s="3">
-        <v>1900</v>
       </c>
       <c r="I24" s="3">
         <v>1400</v>
       </c>
       <c r="J24" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L24" s="3">
         <v>5500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>800</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>1900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>2900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>1600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>1700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>1000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-500</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1847,150 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F26" s="3">
         <v>-5700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-5900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>12800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>3300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>7800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>4800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>28200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>13500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>9900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>4900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>18800</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R26" s="3">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T26" s="3">
         <v>4100</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F27" s="3">
         <v>-5700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-5900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>12800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>3300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>7800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>4800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>28200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>13500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>9900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>4900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>5400</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R27" s="3">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T27" s="3">
         <v>400</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +2051,14 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2119,14 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2187,14 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,132 +2255,150 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>4900</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-5700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>500</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F33" s="3">
         <v>-5700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-5900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>12800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>3300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>7800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>4800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>28200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>13500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>9900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>4900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>5400</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R33" s="3">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T33" s="3">
         <v>400</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2459,155 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F35" s="3">
         <v>-5700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-5900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>12800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>3300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>7800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>4800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>28200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>13500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>9900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>4900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>5400</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R35" s="3">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T35" s="3">
         <v>400</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2630,10 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,53 +2656,55 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>78500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>97700</v>
+      </c>
+      <c r="F41" s="3">
         <v>105500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>79300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>92400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>52200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>51900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>74500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>82500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>89400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>90600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>76600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>81200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>40600</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2547,53 +2720,59 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>96800</v>
+      </c>
+      <c r="E42" s="3">
+        <v>73600</v>
+      </c>
+      <c r="F42" s="3">
         <v>65400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>93900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>82000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>113900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>131100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>100300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>77100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>47400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>31400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>33400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>19800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>14600</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2609,53 +2788,59 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>375500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>291400</v>
+      </c>
+      <c r="F43" s="3">
         <v>258000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>253000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>314300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>277300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>264000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>218400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>286900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>228400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>195400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>173100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>219500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>140500</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2671,8 +2856,14 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2733,53 +2924,59 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>11600</v>
+      </c>
+      <c r="F45" s="3">
         <v>14300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>14200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>14800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>14900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>13100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>11800</v>
-      </c>
-      <c r="J45" s="3">
-        <v>14200</v>
-      </c>
-      <c r="K45" s="3">
-        <v>13000</v>
       </c>
       <c r="L45" s="3">
         <v>14200</v>
       </c>
       <c r="M45" s="3">
+        <v>13000</v>
+      </c>
+      <c r="N45" s="3">
+        <v>14200</v>
+      </c>
+      <c r="O45" s="3">
         <v>8000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>6600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>7500</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2795,53 +2992,59 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>562000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>474400</v>
+      </c>
+      <c r="F46" s="3">
         <v>443200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>440300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>503500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>458200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>460100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>404900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>460700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>378100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>331600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>291100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>327100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>203200</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2857,8 +3060,14 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2919,53 +3128,59 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>81800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>83700</v>
+      </c>
+      <c r="F48" s="3">
         <v>89000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>93400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>97400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>102700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>91600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>71800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>71800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>51900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>43600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>34000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>30000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>27500</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2981,28 +3196,34 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>35800</v>
+      </c>
+      <c r="F49" s="3">
         <v>36200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>36600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>37900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>38700</v>
-      </c>
-      <c r="H49" s="3">
-        <v>6300</v>
-      </c>
-      <c r="I49" s="3">
-        <v>6300</v>
       </c>
       <c r="J49" s="3">
         <v>6300</v>
@@ -3022,11 +3243,11 @@
       <c r="O49" s="3">
         <v>6300</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
+      <c r="P49" s="3">
+        <v>6300</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>6300</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
@@ -3043,8 +3264,14 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3332,14 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,53 +3400,59 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>19100</v>
+      </c>
+      <c r="F52" s="3">
         <v>15200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>7100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>3500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>2600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>12300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>14700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>11500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>2600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>2300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>2200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>7800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>3100</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3229,8 +3468,14 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,53 +3536,59 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>695200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>613000</v>
+      </c>
+      <c r="F54" s="3">
         <v>583700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>577500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>642200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>602200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>570200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>497600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>550200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>438800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>383800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>333500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>371200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>240100</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3353,8 +3604,14 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3634,10 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,53 +3660,55 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>335100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>23900</v>
+      </c>
+      <c r="F57" s="3">
         <v>226600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>6300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>266500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>238400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>19000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>177000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>235400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>185500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>151600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>127200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>176700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>118500</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3463,8 +3724,14 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3525,53 +3792,59 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>44500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>279900</v>
+      </c>
+      <c r="F59" s="3">
         <v>42200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>241300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>35500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>40600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>236500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>23500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>31500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>27500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>24800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>18100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>14800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>11000</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3587,53 +3860,59 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>379600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>303900</v>
+      </c>
+      <c r="F60" s="3">
         <v>268800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>247600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>302000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>279000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>255400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>200600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>267000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>213000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>176400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>145300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>191600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>129600</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3649,8 +3928,14 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3711,53 +3996,59 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>20500</v>
+      </c>
+      <c r="F62" s="3">
         <v>20400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>23500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>28000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>30600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>30900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>29300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>26100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>5000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>5300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>4100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>4200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>2400</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3773,8 +4064,14 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +4132,14 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4200,14 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,53 +4268,59 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>399000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>324400</v>
+      </c>
+      <c r="F66" s="3">
         <v>289100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>271100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>330000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>309600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>286300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>229900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>293000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>218000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>181700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>149400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>195800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>132000</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4021,8 +4336,14 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4366,10 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4430,14 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4498,14 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4208,14 +4543,14 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>61200</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -4231,8 +4566,14 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,53 +4634,59 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>136900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>118200</v>
+      </c>
+      <c r="F72" s="3">
         <v>116400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>122100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>128000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>115200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>111900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>104100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>99300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>71100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>57500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>47600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>42700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>23900</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4355,8 +4702,14 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4770,14 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4838,14 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,53 +4906,59 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>296200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>288600</v>
+      </c>
+      <c r="F76" s="3">
         <v>294500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>306400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>312200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>292600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>283900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>267700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>257200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>220800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>202100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>184100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>175400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>46900</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4603,8 +4974,14 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +5042,155 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F81" s="3">
         <v>-5700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-5900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>12800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>3300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>7800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>4800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>28200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>13500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>9900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>4900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>5400</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R81" s="3">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T81" s="3">
         <v>400</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,50 +5213,52 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>10900</v>
+        <v>11000</v>
       </c>
       <c r="E83" s="3">
         <v>11400</v>
       </c>
       <c r="F83" s="3">
+        <v>10900</v>
+      </c>
+      <c r="G83" s="3">
+        <v>11400</v>
+      </c>
+      <c r="H83" s="3">
         <v>10700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>9100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>7300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>7200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>7100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>6300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>5100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>4600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>4200</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4880,8 +5277,14 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5345,14 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5413,14 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5481,14 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5549,14 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,50 +5617,56 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>23800</v>
+      </c>
+      <c r="F89" s="3">
         <v>15800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>12800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>19400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>28100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>20500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>19300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>28500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>26400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>21100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>12700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>8600</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5252,8 +5685,14 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,50 +5715,52 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-5100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-7400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-12300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-17400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-14800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-4400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-9800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-13000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-13400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-11300</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5338,8 +5779,14 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5847,14 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,50 +5915,56 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-31300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="F94" s="3">
         <v>24400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-18300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>20200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-28000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-45800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-27800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-39600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-28900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-11300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-16800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-18100</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5524,8 +5983,14 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +6013,10 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5610,8 +6077,14 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +6145,14 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +6213,14 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,50 +6281,56 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="F100" s="3">
         <v>-14000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-7600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>2700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>4300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>1200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>4200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>48100</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5858,8 +6349,14 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5920,50 +6417,56 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="F102" s="3">
         <v>26300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-13100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>40200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-22600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-8000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-6900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>14000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-4500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>40600</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5980,6 +6483,12 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PUBM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PUBM_QTR_FIN.xlsx
@@ -656,314 +656,327 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>66700</v>
+      </c>
+      <c r="E8" s="3">
         <v>84600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>63700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>63300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>55400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>74300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>64500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>63000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>54600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>75600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>58100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>49700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>43600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>56200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>37800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>26400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>28300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>34400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>28500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>27400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>23600</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E9" s="3">
         <v>24200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>26100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>25100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>23900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>23000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>21600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>19000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>16900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>11500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>10100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>9300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8800</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E10" s="3">
         <v>60400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>37600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>38200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>31500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>51300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>42900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>44000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>36600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>58700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>42100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>36600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>31300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>44800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>27300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>17200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>18200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>25100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>18900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>19000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>14800</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,76 +1001,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E12" s="3">
         <v>6800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5900</v>
-      </c>
-      <c r="I12" s="3">
-        <v>5100</v>
       </c>
       <c r="J12" s="3">
         <v>5100</v>
       </c>
       <c r="K12" s="3">
+        <v>5100</v>
+      </c>
+      <c r="L12" s="3">
         <v>4800</v>
-      </c>
-      <c r="L12" s="3">
-        <v>4100</v>
       </c>
       <c r="M12" s="3">
         <v>4100</v>
       </c>
       <c r="N12" s="3">
+        <v>4100</v>
+      </c>
+      <c r="O12" s="3">
         <v>3900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3100</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,8 +1141,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1192,8 +1212,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1260,8 +1283,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,65 +1309,66 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>64200</v>
+        <v>72200</v>
       </c>
       <c r="E17" s="3">
         <v>64200</v>
       </c>
       <c r="F17" s="3">
+        <v>64200</v>
+      </c>
+      <c r="G17" s="3">
         <v>70500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>66100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>57800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>54900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>53200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>50000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>47600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>44000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>39500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>37000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>34000</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T17" s="3">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U17" s="3">
         <v>28500</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1351,65 +1378,68 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E18" s="3">
         <v>20400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-7200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-10700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>16500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>9600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>28000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>14100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>10200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>22200</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3">
         <v>5900</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1419,8 +1449,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,65 +1478,66 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E20" s="3">
         <v>2600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4900</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>1600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-500</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1513,65 +1547,68 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E21" s="3">
         <v>34100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>13300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>27500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>13800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>17100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>13400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>40800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>20600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>15000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>11400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>25900</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3">
         <v>18500</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1581,8 +1618,11 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1649,144 +1689,153 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E23" s="3">
         <v>23000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>16800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>33700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>14300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>9900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>21700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2800</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E24" s="3">
         <v>4300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-3400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>800</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>1900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-500</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,65 +1902,68 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E26" s="3">
         <v>18700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>12800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>28200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>13500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>9900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>18800</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T26" s="3">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U26" s="3">
         <v>4100</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1921,65 +1973,68 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E27" s="3">
         <v>18700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>12800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>28200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>13500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>9900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5400</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T27" s="3">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U27" s="3">
         <v>400</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1989,8 +2044,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,65 +2328,68 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4900</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-1600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>500</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2329,65 +2399,68 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E33" s="3">
         <v>18700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>12800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>28200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>13500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>9900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5400</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T33" s="3">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U33" s="3">
         <v>400</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2397,8 +2470,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,65 +2541,68 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E35" s="3">
         <v>18700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>12800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>28200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>13500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>9900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5400</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T35" s="3">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U35" s="3">
         <v>400</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2533,81 +2612,87 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,56 +2744,57 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>80200</v>
+      </c>
+      <c r="E41" s="3">
         <v>78500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>97700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>105500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>79300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>92400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>52200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>51900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>74500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>82500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>89400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>90600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>76600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>81200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>40600</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2726,56 +2813,59 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>93900</v>
+      </c>
+      <c r="E42" s="3">
         <v>96800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>73600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>65400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>93900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>82000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>113900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>131100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>100300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>77100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>47400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>31400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>33400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>19800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>14600</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2794,56 +2884,59 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>303300</v>
+      </c>
+      <c r="E43" s="3">
         <v>375500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>291400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>258000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>253000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>314300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>277300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>264000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>218400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>286900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>228400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>195400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>173100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>219500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>140500</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2862,8 +2955,11 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2930,56 +3026,59 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E45" s="3">
         <v>11100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>11600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>14300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>14200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>14800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>14900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>11800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7500</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2998,56 +3097,59 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>488900</v>
+      </c>
+      <c r="E46" s="3">
         <v>562000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>474400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>443200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>440300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>503500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>458200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>460100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>404900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>460700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>378100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>331600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>291100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>327100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>203200</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3066,8 +3168,11 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3134,56 +3239,59 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E48" s="3">
         <v>81800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>83700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>89000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>93400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>97400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>102700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>91600</v>
-      </c>
-      <c r="K48" s="3">
-        <v>71800</v>
       </c>
       <c r="L48" s="3">
         <v>71800</v>
       </c>
       <c r="M48" s="3">
+        <v>71800</v>
+      </c>
+      <c r="N48" s="3">
         <v>51900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>43600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>34000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>30000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>27500</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3202,31 +3310,34 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E49" s="3">
         <v>35400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>35800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>36200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>36600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>37900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>38700</v>
-      </c>
-      <c r="J49" s="3">
-        <v>6300</v>
       </c>
       <c r="K49" s="3">
         <v>6300</v>
@@ -3249,8 +3360,8 @@
       <c r="Q49" s="3">
         <v>6300</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
+      <c r="R49" s="3">
+        <v>6300</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
@@ -3270,8 +3381,11 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,56 +3523,59 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E52" s="3">
         <v>16000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>19100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>15200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3100</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3474,8 +3594,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,56 +3665,59 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>626200</v>
+      </c>
+      <c r="E54" s="3">
         <v>695200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>613000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>583700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>577500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>642200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>602200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>570200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>497600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>550200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>438800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>383800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>333500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>371200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>240100</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3610,8 +3736,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,56 +3792,57 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>335100</v>
+        <v>13300</v>
       </c>
       <c r="E57" s="3">
+        <v>12600</v>
+      </c>
+      <c r="F57" s="3">
         <v>23900</v>
       </c>
-      <c r="F57" s="3">
-        <v>226600</v>
-      </c>
       <c r="G57" s="3">
+        <v>13500</v>
+      </c>
+      <c r="H57" s="3">
         <v>6300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>266500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>238400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>19000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>177000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>235400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>185500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>151600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>127200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>176700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>118500</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3730,8 +3861,11 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3798,56 +3932,59 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>44500</v>
+        <v>302500</v>
       </c>
       <c r="E59" s="3">
+        <v>367000</v>
+      </c>
+      <c r="F59" s="3">
         <v>279900</v>
       </c>
-      <c r="F59" s="3">
-        <v>42200</v>
-      </c>
       <c r="G59" s="3">
+        <v>255300</v>
+      </c>
+      <c r="H59" s="3">
         <v>241300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>35500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>40600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>236500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>23500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>31500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>27500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>24800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>18100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11000</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,56 +4003,59 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>315800</v>
+      </c>
+      <c r="E60" s="3">
         <v>379600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>303900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>268800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>247600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>302000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>279000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>255400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>200600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>267000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>213000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>176400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>145300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>191600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>129600</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3934,8 +4074,11 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4002,56 +4145,59 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E62" s="3">
         <v>19500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>20500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>20400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>23500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>28000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>30600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>30900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>29300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>26100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2400</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4070,8 +4216,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,56 +4429,59 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>337500</v>
+      </c>
+      <c r="E66" s="3">
         <v>399000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>324400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>289100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>271100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>330000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>309600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>286300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>229900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>293000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>218000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>181700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>149400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>195800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>132000</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4342,8 +4500,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4549,11 +4717,11 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>61200</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,56 +4811,59 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>134400</v>
+      </c>
+      <c r="E72" s="3">
         <v>136900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>118200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>116400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>122100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>128000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>115200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>111900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>104100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>99300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>71100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>57500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>47600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>42700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>23900</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4708,8 +4882,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,56 +5095,59 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>288700</v>
+      </c>
+      <c r="E76" s="3">
         <v>296200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>288600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>294500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>306400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>312200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>292600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>283900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>267700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>257200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>220800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>202100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>184100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>175400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>46900</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4980,8 +5166,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,138 +5237,144 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E81" s="3">
         <v>18700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>12800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>28200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>13500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>9900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5400</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T81" s="3">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U81" s="3">
         <v>400</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5189,8 +5384,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,53 +5413,54 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E83" s="3">
         <v>11000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>11400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>10900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>11400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>10700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4200</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5283,8 +5482,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,53 +5837,56 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E89" s="3">
         <v>28700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>23800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>15800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>12800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>19400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>28100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>20500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>19300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>28500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>26400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>21100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>12700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>8600</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5691,8 +5908,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,53 +5937,54 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-12300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-17400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-14800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-9800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5785,8 +6006,11 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,53 +6148,56 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-31300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>24400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-18300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>20200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-28000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-45800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-27800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-39600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-28900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-11300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-16800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5989,8 +6219,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,53 +6530,56 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-16600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-17800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-14000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>4300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>48100</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6355,8 +6601,11 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6423,53 +6672,56 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-19200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>26300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-13100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>40200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-22600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>14000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>40600</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6489,6 +6741,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PUBM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PUBM_QTR_FIN.xlsx
@@ -656,327 +656,340 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>67300</v>
+      </c>
+      <c r="E8" s="3">
         <v>66700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>84600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>63700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>63300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>55400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>74300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>64500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>63000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>54600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>75600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>58100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>49700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>43600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>56200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>37800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>26400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>28300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>34400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>28500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>27400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>23600</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E9" s="3">
         <v>25400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>24200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>26100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>25100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>23900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>23000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>21600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>19000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>16000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>13100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>11500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8800</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>42100</v>
+      </c>
+      <c r="E10" s="3">
         <v>41300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>60400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>37600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>38200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>31500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>51300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>42900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>44000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>36600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>58700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>42100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>36600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>31300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>44800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>27300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>17200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>18200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>25100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>18900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>19000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>14800</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,79 +1015,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E12" s="3">
         <v>8000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5900</v>
-      </c>
-      <c r="J12" s="3">
-        <v>5100</v>
       </c>
       <c r="K12" s="3">
         <v>5100</v>
       </c>
       <c r="L12" s="3">
+        <v>5100</v>
+      </c>
+      <c r="M12" s="3">
         <v>4800</v>
-      </c>
-      <c r="M12" s="3">
-        <v>4100</v>
       </c>
       <c r="N12" s="3">
         <v>4100</v>
       </c>
       <c r="O12" s="3">
+        <v>4100</v>
+      </c>
+      <c r="P12" s="3">
         <v>3900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>3100</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,8 +1161,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1215,8 +1235,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1286,8 +1309,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,68 +1336,69 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>71300</v>
+      </c>
+      <c r="E17" s="3">
         <v>72200</v>
-      </c>
-      <c r="E17" s="3">
-        <v>64200</v>
       </c>
       <c r="F17" s="3">
         <v>64200</v>
       </c>
       <c r="G17" s="3">
+        <v>64200</v>
+      </c>
+      <c r="H17" s="3">
         <v>70500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>66100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>57800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>54900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>53200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>50000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>47600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>44000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>39500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>37000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>34000</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V17" s="3">
         <v>28500</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1381,68 +1408,71 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>20400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-7200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-10700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>16500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>28000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>14100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>10200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>22200</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3">
         <v>5900</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1452,8 +1482,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,68 +1512,69 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E20" s="3">
         <v>2800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4900</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>1600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-500</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1550,68 +1584,71 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E21" s="3">
         <v>8500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>34100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>13300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>27500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>13800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>17100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>13400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>40800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>20600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>15000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>11400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>25900</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3">
         <v>18500</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1621,8 +1658,11 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1692,150 +1732,159 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>23000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>16800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>33700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>14300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>9900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>21700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>5800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-3400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>800</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>1900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-500</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,68 +1954,71 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>18700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>12800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>28200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>13500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>9900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>18800</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V26" s="3">
         <v>4100</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1976,68 +2028,71 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>18700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>12800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>28200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>13500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>9900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5400</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V27" s="3">
         <v>400</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2047,8 +2102,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2250,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,68 +2398,71 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4900</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-1600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>500</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2402,68 +2472,71 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>18700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>12800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>28200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>13500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>9900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5400</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V33" s="3">
         <v>400</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2473,8 +2546,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,68 +2620,71 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>18700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>12800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>28200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>13500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>9900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5400</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V35" s="3">
         <v>400</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2615,84 +2694,90 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,59 +2831,60 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>73500</v>
+      </c>
+      <c r="E41" s="3">
         <v>80200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>78500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>97700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>105500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>79300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>92400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>52200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>51900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>74500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>82500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>89400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>90600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>76600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>81200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>40600</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2816,59 +2903,62 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>92100</v>
+      </c>
+      <c r="E42" s="3">
         <v>93900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>96800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>73600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>65400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>93900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>82000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>113900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>131100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>100300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>77100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>47400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>31400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>33400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>19800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>14600</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2887,59 +2977,62 @@
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>351600</v>
+      </c>
+      <c r="E43" s="3">
         <v>303300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>375500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>291400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>258000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>253000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>314300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>277300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>264000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>218400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>286900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>228400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>195400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>173100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>219500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>140500</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2958,8 +3051,11 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3029,59 +3125,62 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E45" s="3">
         <v>11500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>11100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>11600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>14300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>14200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>14800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>14900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>7500</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3100,59 +3199,62 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>532000</v>
+      </c>
+      <c r="E46" s="3">
         <v>488900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>562000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>474400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>443200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>440300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>503500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>458200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>460100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>404900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>460700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>378100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>331600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>291100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>327100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>203200</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3171,8 +3273,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3242,59 +3347,62 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>82100</v>
+      </c>
+      <c r="E48" s="3">
         <v>80000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>81800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>83700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>89000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>93400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>97400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>102700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>91600</v>
-      </c>
-      <c r="L48" s="3">
-        <v>71800</v>
       </c>
       <c r="M48" s="3">
         <v>71800</v>
       </c>
       <c r="N48" s="3">
+        <v>71800</v>
+      </c>
+      <c r="O48" s="3">
         <v>51900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>43600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>34000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>30000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>27500</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3313,34 +3421,37 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E49" s="3">
         <v>35000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>35400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>35800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>36200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>36600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>37900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>38700</v>
-      </c>
-      <c r="K49" s="3">
-        <v>6300</v>
       </c>
       <c r="L49" s="3">
         <v>6300</v>
@@ -3363,8 +3474,8 @@
       <c r="R49" s="3">
         <v>6300</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
+      <c r="S49" s="3">
+        <v>6300</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
@@ -3384,8 +3495,11 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,59 +3643,62 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E52" s="3">
         <v>22200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>16000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>19100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>15200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>11500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3100</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3597,8 +3717,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,59 +3791,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>673100</v>
+      </c>
+      <c r="E54" s="3">
         <v>626200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>695200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>613000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>583700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>577500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>642200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>602200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>570200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>497600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>550200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>438800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>383800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>333500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>371200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>240100</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3739,8 +3865,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,59 +3923,60 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E57" s="3">
         <v>13300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>23900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>266500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>238400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>19000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>177000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>235400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>185500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>151600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>127200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>176700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>118500</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,8 +3995,11 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3935,59 +4069,62 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>346900</v>
+      </c>
+      <c r="E59" s="3">
         <v>302500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>367000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>279900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>255300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>241300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>35500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>40600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>236500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>23500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>31500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>27500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>24800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11000</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4006,59 +4143,62 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>370100</v>
+      </c>
+      <c r="E60" s="3">
         <v>315800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>379600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>303900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>268800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>247600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>302000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>279000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>255400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>200600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>267000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>213000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>176400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>145300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>191600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>129600</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4077,8 +4217,11 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4148,59 +4291,62 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E62" s="3">
         <v>21700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>19500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>20500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>20400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>23500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>28000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>30600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>30900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>29300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>26100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2400</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4219,8 +4365,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,59 +4587,62 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>390400</v>
+      </c>
+      <c r="E66" s="3">
         <v>337500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>399000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>324400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>289100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>271100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>330000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>309600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>286300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>229900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>293000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>218000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>181700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>149400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>195800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>132000</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4503,8 +4661,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4720,11 +4888,11 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>61200</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,59 +4985,62 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>136400</v>
+      </c>
+      <c r="E72" s="3">
         <v>134400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>136900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>118200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>116400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>122100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>128000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>115200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>111900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>104100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>99300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>71100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>57500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>47600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>42700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>23900</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4885,8 +5059,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,59 +5281,62 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>282700</v>
+      </c>
+      <c r="E76" s="3">
         <v>288700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>296200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>288600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>294500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>306400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>312200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>292600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>283900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>267700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>257200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>220800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>202100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>184100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>175400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>46900</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5169,8 +5355,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,144 +5429,150 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>18700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>12800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>28200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>13500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>9900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5400</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V81" s="3">
         <v>400</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5387,8 +5582,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,56 +5612,57 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E83" s="3">
         <v>11200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>11000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>10900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>11400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>10700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>9100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4200</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5485,8 +5684,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,56 +6054,59 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E89" s="3">
         <v>24300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>28700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>23800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>15800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>12800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>19400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>28100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>20500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>19300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>28500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>26400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>21100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>12700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>8600</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5911,8 +6128,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,56 +6158,57 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-12300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-17400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-14800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11300</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6009,8 +6230,11 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,56 +6378,59 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-31300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>24400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-18300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>20200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-28000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-45800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-27800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-39600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-28900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-18100</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6222,8 +6452,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6482,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6320,8 +6554,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,56 +6776,59 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-18700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-16600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-17800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-14000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>4300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>4200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>48100</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6604,8 +6850,11 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6675,56 +6924,59 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E102" s="3">
         <v>1700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-19200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-7800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>26300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-13100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>40200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-22600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>14000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>40600</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6744,6 +6996,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PUBM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PUBM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="92">
   <si>
     <t>PUBM</t>
   </si>
@@ -656,340 +656,353 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>71800</v>
+      </c>
+      <c r="E8" s="3">
         <v>67300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>66700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>84600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>63700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>63300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>55400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>74300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>64500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>63000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>54600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>75600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>58100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>49700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>43600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>56200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>37800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>26400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>28300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>34400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>28500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>27400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>23600</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E9" s="3">
         <v>25200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>25400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>24200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>26100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>25100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>23900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>23000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>21600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>19000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>16900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>16000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>13100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>11500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>10500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>9200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>10100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8800</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E10" s="3">
         <v>42100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>41300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>60400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>37600</v>
       </c>
-      <c r="H10" s="3">
-        <v>38200</v>
-      </c>
       <c r="I10" s="3">
+        <v>38300</v>
+      </c>
+      <c r="J10" s="3">
         <v>31500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>51300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>42900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>44000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>36600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>58700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>42100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>36600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>31300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>44800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>27300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>17200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>18200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>25100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>18900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>19000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>14800</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,82 +1029,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E12" s="3">
         <v>8700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5900</v>
-      </c>
-      <c r="K12" s="3">
-        <v>5100</v>
       </c>
       <c r="L12" s="3">
         <v>5100</v>
       </c>
       <c r="M12" s="3">
+        <v>5100</v>
+      </c>
+      <c r="N12" s="3">
         <v>4800</v>
-      </c>
-      <c r="N12" s="3">
-        <v>4100</v>
       </c>
       <c r="O12" s="3">
         <v>4100</v>
       </c>
       <c r="P12" s="3">
+        <v>4100</v>
+      </c>
+      <c r="Q12" s="3">
         <v>3900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>3300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>3100</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,31 +1181,34 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1238,31 +1258,34 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>6700</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>8600</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1312,8 +1335,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,71 +1363,72 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>73200</v>
+      </c>
+      <c r="E17" s="3">
         <v>71300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>72200</v>
-      </c>
-      <c r="F17" s="3">
-        <v>64200</v>
       </c>
       <c r="G17" s="3">
         <v>64200</v>
       </c>
       <c r="H17" s="3">
+        <v>64200</v>
+      </c>
+      <c r="I17" s="3">
         <v>70500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>66100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>57800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>54900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>53200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>50000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>47600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>44000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>39500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>37000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>34000</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V17" s="3">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W17" s="3">
         <v>28500</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1411,71 +1438,74 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-5500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>20400</v>
       </c>
-      <c r="G18" s="3">
-        <v>-500</v>
-      </c>
       <c r="H18" s="3">
-        <v>-7200</v>
+        <v>-600</v>
       </c>
       <c r="I18" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="J18" s="3">
         <v>-10700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>16500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>28000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>14100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>10200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>22200</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3">
         <v>5900</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1485,8 +1515,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,71 +1546,72 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>6300</v>
+        <v>900</v>
       </c>
       <c r="E20" s="3">
-        <v>2800</v>
+        <v>-4000</v>
       </c>
       <c r="F20" s="3">
-        <v>2600</v>
+        <v>-300</v>
       </c>
       <c r="G20" s="3">
-        <v>2400</v>
+        <v>-100</v>
       </c>
       <c r="H20" s="3">
-        <v>2000</v>
+        <v>-200</v>
       </c>
       <c r="I20" s="3">
-        <v>1400</v>
+        <v>200</v>
       </c>
       <c r="J20" s="3">
+        <v>500</v>
+      </c>
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4900</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>1600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-500</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1587,71 +1621,74 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>13700</v>
+        <v>4200</v>
       </c>
       <c r="E21" s="3">
-        <v>8500</v>
+        <v>6800</v>
       </c>
       <c r="F21" s="3">
-        <v>34100</v>
+        <v>1700</v>
       </c>
       <c r="G21" s="3">
-        <v>13300</v>
+        <v>27600</v>
       </c>
       <c r="H21" s="3">
-        <v>5700</v>
+        <v>7200</v>
       </c>
       <c r="I21" s="3">
-        <v>2200</v>
+        <v>200</v>
       </c>
       <c r="J21" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="K21" s="3">
         <v>27500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>13800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>17100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>13400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>40800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>20600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>15000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>11400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>25900</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3">
         <v>18500</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1661,31 +1698,34 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1735,156 +1775,165 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E23" s="3">
         <v>2400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>23000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>16800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>9700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>33700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>14300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>9900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>21700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>5800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-3400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>800</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>1900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-500</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,71 +2006,74 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E26" s="3">
         <v>2000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>18700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>12800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>28200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>13500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>9900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>18800</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V26" s="3">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W26" s="3">
         <v>4100</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2031,71 +2083,74 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E27" s="3">
         <v>2000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>18700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>12800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>28200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>13500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>9900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5400</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V27" s="3">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W27" s="3">
         <v>400</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2105,8 +2160,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2237,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2314,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2391,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,71 +2468,74 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-6300</v>
+        <v>-900</v>
       </c>
       <c r="E32" s="3">
-        <v>-2800</v>
+        <v>4000</v>
       </c>
       <c r="F32" s="3">
-        <v>-2600</v>
+        <v>300</v>
       </c>
       <c r="G32" s="3">
-        <v>-2400</v>
+        <v>100</v>
       </c>
       <c r="H32" s="3">
-        <v>-2000</v>
+        <v>200</v>
       </c>
       <c r="I32" s="3">
-        <v>-1400</v>
+        <v>-200</v>
       </c>
       <c r="J32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4900</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-1600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>500</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2475,71 +2545,74 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E33" s="3">
         <v>2000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>18700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>12800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>28200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>13500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>9900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5400</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V33" s="3">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W33" s="3">
         <v>400</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2549,8 +2622,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,71 +2699,74 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E35" s="3">
         <v>2000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>18700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>12800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>28200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>13500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>9900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5400</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V35" s="3">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W35" s="3">
         <v>400</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2697,87 +2776,93 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2889,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,62 +2918,63 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>78900</v>
+      </c>
+      <c r="E41" s="3">
         <v>73500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>80200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>78500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>97700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>105500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>79300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>92400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>52200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>51900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>74500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>82500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>89400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>90600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>76600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>81200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>40600</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2906,62 +2993,65 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>61500</v>
+      </c>
+      <c r="E42" s="3">
         <v>92100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>93900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>96800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>73600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>65400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>93900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>82000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>113900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>131100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>100300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>77100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>47400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>31400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>33400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>19800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>14600</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2980,62 +3070,65 @@
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>376800</v>
+      </c>
+      <c r="E43" s="3">
         <v>351600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>303300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>375500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>291400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>258000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>253000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>314300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>277300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>264000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>218400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>286900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>228400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>195400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>173100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>219500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>140500</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3054,31 +3147,34 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3128,62 +3224,65 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>14800</v>
       </c>
-      <c r="E45" s="3">
-        <v>11500</v>
-      </c>
-      <c r="F45" s="3">
-        <v>11100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>11600</v>
-      </c>
-      <c r="H45" s="3">
-        <v>14300</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="L45" s="3">
+        <v>14900</v>
+      </c>
+      <c r="M45" s="3">
+        <v>13100</v>
+      </c>
+      <c r="N45" s="3">
+        <v>11800</v>
+      </c>
+      <c r="O45" s="3">
         <v>14200</v>
       </c>
-      <c r="J45" s="3">
-        <v>14800</v>
-      </c>
-      <c r="K45" s="3">
-        <v>14900</v>
-      </c>
-      <c r="L45" s="3">
-        <v>13100</v>
-      </c>
-      <c r="M45" s="3">
-        <v>11800</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
+        <v>13000</v>
+      </c>
+      <c r="Q45" s="3">
         <v>14200</v>
       </c>
-      <c r="O45" s="3">
-        <v>13000</v>
-      </c>
-      <c r="P45" s="3">
-        <v>14200</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>8000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7500</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3202,62 +3301,65 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>529800</v>
+      </c>
+      <c r="E46" s="3">
         <v>532000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>488900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>562000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>474400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>443200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>440300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>503500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>458200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>460100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>404900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>460700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>378100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>331600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>291100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>327100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>203200</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3276,31 +3378,34 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3350,62 +3455,65 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>97700</v>
+      </c>
+      <c r="E48" s="3">
         <v>82100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>80000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>81800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>83700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>89000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>93400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>97400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>102700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>91600</v>
-      </c>
-      <c r="M48" s="3">
-        <v>71800</v>
       </c>
       <c r="N48" s="3">
         <v>71800</v>
       </c>
       <c r="O48" s="3">
+        <v>71800</v>
+      </c>
+      <c r="P48" s="3">
         <v>51900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>43600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>34000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>30000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>27500</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3424,37 +3532,40 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E49" s="3">
         <v>34700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>35000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>35400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>35800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>36200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>36600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>37900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>38700</v>
-      </c>
-      <c r="L49" s="3">
-        <v>6300</v>
       </c>
       <c r="M49" s="3">
         <v>6300</v>
@@ -3477,8 +3588,8 @@
       <c r="S49" s="3">
         <v>6300</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
+      <c r="T49" s="3">
+        <v>6300</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
@@ -3498,8 +3609,11 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3686,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,62 +3763,65 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>24400</v>
+        <v>2700</v>
       </c>
       <c r="E52" s="3">
-        <v>22200</v>
+        <v>1800</v>
       </c>
       <c r="F52" s="3">
-        <v>16000</v>
+        <v>3700</v>
       </c>
       <c r="G52" s="3">
-        <v>19100</v>
+        <v>2100</v>
       </c>
       <c r="H52" s="3">
-        <v>15200</v>
+        <v>4400</v>
       </c>
       <c r="I52" s="3">
-        <v>7100</v>
+        <v>2000</v>
       </c>
       <c r="J52" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K52" s="3">
         <v>3500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3100</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3720,8 +3840,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,62 +3917,65 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>689100</v>
+      </c>
+      <c r="E54" s="3">
         <v>673100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>626200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>695200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>613000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>583700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>577500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>642200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>602200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>570200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>497600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>550200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>438800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>383800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>333500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>371200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>240100</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3868,8 +3994,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4025,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,62 +4054,63 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>23200</v>
+        <v>360700</v>
       </c>
       <c r="E57" s="3">
-        <v>13300</v>
+        <v>340800</v>
       </c>
       <c r="F57" s="3">
-        <v>12600</v>
+        <v>289200</v>
       </c>
       <c r="G57" s="3">
-        <v>23900</v>
+        <v>347700</v>
       </c>
       <c r="H57" s="3">
-        <v>13500</v>
+        <v>273200</v>
       </c>
       <c r="I57" s="3">
-        <v>6300</v>
+        <v>240100</v>
       </c>
       <c r="J57" s="3">
+        <v>222600</v>
+      </c>
+      <c r="K57" s="3">
         <v>266500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>238400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>19000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>177000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>235400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>185500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>151600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>127200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>176700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>118500</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3998,31 +4129,34 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4072,62 +4206,65 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>346900</v>
-      </c>
-      <c r="E59" s="3">
-        <v>302500</v>
-      </c>
-      <c r="F59" s="3">
-        <v>367000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>279900</v>
-      </c>
-      <c r="H59" s="3">
-        <v>255300</v>
-      </c>
-      <c r="I59" s="3">
-        <v>241300</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>35500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>40600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>236500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>23500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>31500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>27500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>24800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>18100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>14800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11000</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4146,62 +4283,65 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>392800</v>
+      </c>
+      <c r="E60" s="3">
         <v>370100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>315800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>379600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>303900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>268800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>247600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>302000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>279000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>255400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>200600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>267000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>213000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>176400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>145300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>191600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>129600</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4220,31 +4360,34 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>29500</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>16700</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>18100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>16100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>17400</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>18800</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>20400</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4294,62 +4437,65 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>20300</v>
+        <v>3700</v>
       </c>
       <c r="E62" s="3">
-        <v>21700</v>
+        <v>3600</v>
       </c>
       <c r="F62" s="3">
-        <v>19500</v>
+        <v>3600</v>
       </c>
       <c r="G62" s="3">
-        <v>20500</v>
+        <v>3400</v>
       </c>
       <c r="H62" s="3">
-        <v>20400</v>
+        <v>3100</v>
       </c>
       <c r="I62" s="3">
-        <v>23500</v>
+        <v>1600</v>
       </c>
       <c r="J62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K62" s="3">
         <v>28000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>30600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>30900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>29300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>26100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2400</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4368,8 +4514,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4591,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4668,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,62 +4745,65 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>425900</v>
+      </c>
+      <c r="E66" s="3">
         <v>390400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>337500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>399000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>324400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>289100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>271100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>330000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>309600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>286300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>229900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>293000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>218000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>181700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>149400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>195800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>132000</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4664,8 +4822,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4853,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4928,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5005,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4891,11 +5059,11 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>61200</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4914,8 +5082,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,62 +5159,65 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>135500</v>
+      </c>
+      <c r="E72" s="3">
         <v>136400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>134400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>136900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>118200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>116400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>122100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>128000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>115200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>111900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>104100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>99300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>71100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>57500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>47600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>42700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>23900</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5062,8 +5236,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5313,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5390,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,62 +5467,65 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>263200</v>
+      </c>
+      <c r="E76" s="3">
         <v>282700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>288700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>296200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>288600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>294500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>306400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>312200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>292600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>283900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>267700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>257200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>220800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>202100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>184100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>175400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>46900</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5358,8 +5544,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,150 +5621,156 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E81" s="3">
         <v>2000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>18700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>12800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>28200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>13500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>9900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5400</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V81" s="3">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W81" s="3">
         <v>400</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5585,8 +5780,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,59 +5811,60 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>11300</v>
+        <v>7200</v>
       </c>
       <c r="E83" s="3">
-        <v>11200</v>
+        <v>6000</v>
       </c>
       <c r="F83" s="3">
-        <v>11000</v>
+        <v>8600</v>
       </c>
       <c r="G83" s="3">
-        <v>11400</v>
+        <v>7400</v>
       </c>
       <c r="H83" s="3">
-        <v>10900</v>
+        <v>6400</v>
       </c>
       <c r="I83" s="3">
-        <v>11400</v>
+        <v>4900</v>
       </c>
       <c r="J83" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K83" s="3">
         <v>10700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>9100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4200</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5687,8 +5886,11 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5963,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6040,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6117,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6194,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,59 +6271,62 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E89" s="3">
         <v>11900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>24300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>28700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>23800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>15800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>12800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>19400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>28100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>20500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>19300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>28500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>26400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>21100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>12700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>8600</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6131,8 +6348,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,59 +6379,60 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-5000</v>
+        <v>-11700</v>
       </c>
       <c r="E91" s="3">
-        <v>-8000</v>
+        <v>-700</v>
       </c>
       <c r="F91" s="3">
-        <v>-9100</v>
+        <v>-800</v>
       </c>
       <c r="G91" s="3">
-        <v>-6700</v>
+        <v>-5200</v>
       </c>
       <c r="H91" s="3">
-        <v>-5100</v>
+        <v>-2900</v>
       </c>
       <c r="I91" s="3">
-        <v>-7400</v>
+        <v>-1100</v>
       </c>
       <c r="J91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K91" s="3">
         <v>-12300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-17400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-14800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-9800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11300</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6233,8 +6454,11 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6531,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,59 +6608,62 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-31300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>24400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-18300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>20200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-28000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-45800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-27800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-39600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-28900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-16800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-18100</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6455,8 +6685,11 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,31 +6716,32 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6557,8 +6791,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6868,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6945,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,59 +7022,62 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-29300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-16600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-18700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-16600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-17800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-14000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>48100</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6853,31 +7099,34 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6927,59 +7176,62 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-19200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-7800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>26300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-13100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>40200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-22600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>14000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>40600</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6999,6 +7251,9 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PUBM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PUBM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="92">
   <si>
     <t>PUBM</t>
   </si>
@@ -656,353 +656,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>85500</v>
+      </c>
+      <c r="E8" s="3">
         <v>71800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>67300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>66700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>84600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>63700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>63300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>55400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>74300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>64500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>63000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>54600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>75600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>58100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>49700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>43600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>56200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>37800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>26400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>28300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>34400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>28500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>27400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>23600</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E9" s="3">
         <v>25500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>25200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>25400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>24200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>26100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>25100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>23900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>23000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>21600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>19000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>18000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>16900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>16000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>11500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>10100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8800</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E10" s="3">
         <v>46300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>42100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>41300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>60400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>37600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>38300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>31500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>51300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>42900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>44000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>36600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>58700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>42100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>36600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>31300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>44800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>27300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>17200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>18200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>25100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>18900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>19000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>14800</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1030,85 +1042,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E12" s="3">
         <v>8800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5900</v>
-      </c>
-      <c r="L12" s="3">
-        <v>5100</v>
       </c>
       <c r="M12" s="3">
         <v>5100</v>
       </c>
       <c r="N12" s="3">
+        <v>5100</v>
+      </c>
+      <c r="O12" s="3">
         <v>4800</v>
-      </c>
-      <c r="O12" s="3">
-        <v>4100</v>
       </c>
       <c r="P12" s="3">
         <v>4100</v>
       </c>
       <c r="Q12" s="3">
+        <v>4100</v>
+      </c>
+      <c r="R12" s="3">
         <v>3900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>3000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>3300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3100</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,8 +1200,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1210,8 +1229,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1261,35 +1280,38 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E15" s="3">
         <v>6500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>6700</v>
-      </c>
-      <c r="F15" s="3">
-        <v>7000</v>
       </c>
       <c r="G15" s="3">
         <v>7000</v>
       </c>
       <c r="H15" s="3">
-        <v>7600</v>
+        <v>7000</v>
       </c>
       <c r="I15" s="3">
         <v>7600</v>
       </c>
       <c r="J15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="K15" s="3">
         <v>8600</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1338,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,74 +1389,75 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>70700</v>
+      </c>
+      <c r="E17" s="3">
         <v>73200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>71300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>72200</v>
-      </c>
-      <c r="G17" s="3">
-        <v>64200</v>
       </c>
       <c r="H17" s="3">
         <v>64200</v>
       </c>
       <c r="I17" s="3">
+        <v>64200</v>
+      </c>
+      <c r="J17" s="3">
         <v>70500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>66100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>57800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>54900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>53200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>50000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>47600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>44000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>39500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>37000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>34000</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X17" s="3">
         <v>28500</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1441,74 +1467,77 @@
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>20400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-10700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>16500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>28000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>14100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>10200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>6600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>22200</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3">
         <v>5900</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1518,8 +1547,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,74 +1579,75 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E20" s="3">
         <v>900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4900</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>1600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-500</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1624,74 +1657,77 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E21" s="3">
         <v>4200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>27600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>27500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>13800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>17100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>13400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>40800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>20600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>15000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>11400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>25900</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3">
         <v>18500</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1701,8 +1737,11 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1727,8 +1766,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1778,162 +1817,171 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>23000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-9200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>16800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>9700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>33700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>14300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>9900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>21700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>7900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>5800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-3400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>800</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>1900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-500</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,74 +2057,77 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>18700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>12800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>28200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>13500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>9900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>18800</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X26" s="3">
         <v>4100</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2086,74 +2137,77 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>18700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>12800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>28200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>13500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>9900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5400</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X27" s="3">
         <v>400</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2163,8 +2217,11 @@
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2317,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,74 +2537,77 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4900</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-1600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>500</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2548,74 +2617,77 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>18700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>12800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>28200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>13500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>9900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5400</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X33" s="3">
         <v>400</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2625,8 +2697,11 @@
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,74 +2777,77 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>18700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>12800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>28200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>13500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>9900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5400</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X35" s="3">
         <v>400</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2779,90 +2857,96 @@
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,65 +3004,66 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>100500</v>
+      </c>
+      <c r="E41" s="3">
         <v>78900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>73500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>80200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>78500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>97700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>105500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>79300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>92400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>52200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>51900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>74500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>82500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>89400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>90600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>76600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>81200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>40600</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2996,65 +3082,68 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E42" s="3">
         <v>61500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>92100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>93900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>96800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>73600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>65400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>93900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>82000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>113900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>131100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>100300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>77100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>47400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>31400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>33400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>19800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>14600</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3073,65 +3162,68 @@
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>424800</v>
+      </c>
+      <c r="E43" s="3">
         <v>376800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>351600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>303300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>375500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>291400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>258000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>253000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>314300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>277300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>264000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>218400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>286900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>228400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>195400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>173100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>219500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>140500</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3150,8 +3242,11 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3176,8 +3271,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3227,8 +3322,11 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3253,39 +3351,39 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>14800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>11800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>14200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>8000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7500</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3304,65 +3402,68 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>575500</v>
+      </c>
+      <c r="E46" s="3">
         <v>529800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>532000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>488900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>562000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>474400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>443200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>440300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>503500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>458200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>460100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>404900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>460700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>378100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>331600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>291100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>327100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>203200</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3381,8 +3482,11 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3407,8 +3511,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3458,65 +3562,68 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>102900</v>
+      </c>
+      <c r="E48" s="3">
         <v>97700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>82100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>80000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>81800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>83700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>89000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>93400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>97400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>102700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>91600</v>
-      </c>
-      <c r="N48" s="3">
-        <v>71800</v>
       </c>
       <c r="O48" s="3">
         <v>71800</v>
       </c>
       <c r="P48" s="3">
+        <v>71800</v>
+      </c>
+      <c r="Q48" s="3">
         <v>51900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>43600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>34000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>30000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>27500</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3535,40 +3642,43 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E49" s="3">
         <v>34300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>34700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>35000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>35400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>35800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>36200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>36600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>37900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>38700</v>
-      </c>
-      <c r="M49" s="3">
-        <v>6300</v>
       </c>
       <c r="N49" s="3">
         <v>6300</v>
@@ -3591,8 +3701,8 @@
       <c r="T49" s="3">
         <v>6300</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
+      <c r="U49" s="3">
+        <v>6300</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
@@ -3612,8 +3722,11 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,65 +3882,68 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E52" s="3">
         <v>2700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3100</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3843,8 +3962,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,65 +4042,68 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>739500</v>
+      </c>
+      <c r="E54" s="3">
         <v>689100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>673100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>626200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>695200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>613000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>583700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>577500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>642200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>602200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>570200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>497600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>550200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>438800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>383800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>333500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>371200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>240100</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3997,8 +4122,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,65 +4184,66 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>386600</v>
+      </c>
+      <c r="E57" s="3">
         <v>360700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>340800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>289200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>347700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>273200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>240100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>222600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>266500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>238400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>19000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>177000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>235400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>185500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>151600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>127200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>176700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>118500</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4132,35 +4262,38 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E58" s="3">
         <v>6400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5800</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -4209,8 +4342,11 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4235,39 +4371,39 @@
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3">
         <v>35500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>40600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>236500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>23500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>31500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>27500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>24800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>18100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>14800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11000</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4286,65 +4422,68 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>418800</v>
+      </c>
+      <c r="E60" s="3">
         <v>392800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>370100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>315800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>379600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>303900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>268800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>247600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>302000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>279000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>255400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>200600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>267000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>213000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>176400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>145300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>191600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>129600</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4363,35 +4502,38 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E61" s="3">
         <v>29500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>16700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>16100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>17400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>18800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>20400</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -4440,65 +4582,68 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E62" s="3">
         <v>3700</v>
-      </c>
-      <c r="E62" s="3">
-        <v>3600</v>
       </c>
       <c r="F62" s="3">
         <v>3600</v>
       </c>
       <c r="G62" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H62" s="3">
         <v>3400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>28000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>30600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>30900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>29300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>26100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2400</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4517,8 +4662,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,65 +4902,68 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>462300</v>
+      </c>
+      <c r="E66" s="3">
         <v>425900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>390400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>337500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>399000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>324400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>289100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>271100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>330000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>309600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>286300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>229900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>293000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>218000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>181700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>149400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>195800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>132000</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4825,8 +4982,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5062,11 +5229,11 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>61200</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -5085,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,65 +5332,68 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>149400</v>
+      </c>
+      <c r="E72" s="3">
         <v>135500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>136400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>134400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>136900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>118200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>116400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>122100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>128000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>115200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>111900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>104100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>99300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>71100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>57500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>47600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>42700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>23900</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5239,8 +5412,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,65 +5652,68 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>277300</v>
+      </c>
+      <c r="E76" s="3">
         <v>263200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>282700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>288700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>296200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>288600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>294500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>306400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>312200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>292600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>283900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>267700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>257200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>220800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>202100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>184100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>175400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>46900</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5547,8 +5732,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,156 +5812,162 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>18700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>12800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>28200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>13500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>9900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5400</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X81" s="3">
         <v>400</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5783,8 +5977,11 @@
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,62 +6009,63 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E83" s="3">
         <v>7200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>8600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>10700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>9100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4200</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5889,8 +6087,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,62 +6487,65 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E89" s="3">
         <v>19100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>24300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>28700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>23800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>15800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>12800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>19400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>28100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>20500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>19300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>28500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>26400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>21100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>12700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>8600</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6351,8 +6567,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,62 +6599,63 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-17400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-14800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-9800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-11300</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6457,8 +6677,11 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,62 +6837,65 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E94" s="3">
         <v>15500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-31300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>24400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-18300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>20200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-28000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-45800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-27800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-39600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-28900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-11300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-16800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-18100</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6688,8 +6917,11 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6743,8 +6976,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6794,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,62 +7267,65 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-29300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-16600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-18700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-16600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-17800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-14000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>4300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>4200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>48100</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7102,8 +7347,11 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7128,8 +7376,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -7179,62 +7427,65 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E102" s="3">
         <v>5400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-19200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>26300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-13100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>40200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-22600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>14000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>40600</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7254,6 +7505,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PUBM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PUBM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="92">
   <si>
     <t>PUBM</t>
   </si>
@@ -656,365 +656,378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>63800</v>
+      </c>
+      <c r="E8" s="3">
         <v>85500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>71800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>67300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>66700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>84600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>63700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>63300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>55400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>74300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>64500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>63000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>54600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>75600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>58100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>49700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>43600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>56200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>37800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>26400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>28300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>34400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>28500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>27400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>23600</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E9" s="3">
         <v>24900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>25500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>25200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>25400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>24200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>26100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>25100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>23900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>23000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>21600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>19000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>18000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>16900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>16000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>13100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>11500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>10500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>10100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>9600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8800</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E10" s="3">
         <v>60600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>46300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>42100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>41300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>60400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>37600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>38300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>31500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>51300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>42900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>44000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>36600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>58700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>42100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>36600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>31300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>44800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>27300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>17200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>18200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>25100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>18900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>19000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>14800</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1043,88 +1056,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E12" s="3">
         <v>7800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>8000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5900</v>
-      </c>
-      <c r="M12" s="3">
-        <v>5100</v>
       </c>
       <c r="N12" s="3">
         <v>5100</v>
       </c>
       <c r="O12" s="3">
+        <v>5100</v>
+      </c>
+      <c r="P12" s="3">
         <v>4800</v>
-      </c>
-      <c r="P12" s="3">
-        <v>4100</v>
       </c>
       <c r="Q12" s="3">
         <v>4100</v>
       </c>
       <c r="R12" s="3">
+        <v>4100</v>
+      </c>
+      <c r="S12" s="3">
         <v>3900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>3100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>3000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>3100</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,8 +1220,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1232,8 +1252,8 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1283,8 +1303,11 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1292,29 +1315,29 @@
         <v>6200</v>
       </c>
       <c r="E15" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F15" s="3">
         <v>6500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6700</v>
-      </c>
-      <c r="G15" s="3">
-        <v>7000</v>
       </c>
       <c r="H15" s="3">
         <v>7000</v>
       </c>
       <c r="I15" s="3">
-        <v>7600</v>
+        <v>7000</v>
       </c>
       <c r="J15" s="3">
         <v>7600</v>
       </c>
       <c r="K15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="L15" s="3">
         <v>8600</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1363,8 +1386,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,77 +1416,78 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>75700</v>
+      </c>
+      <c r="E17" s="3">
         <v>70700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>73200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>71300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>72200</v>
-      </c>
-      <c r="H17" s="3">
-        <v>64200</v>
       </c>
       <c r="I17" s="3">
         <v>64200</v>
       </c>
       <c r="J17" s="3">
+        <v>64200</v>
+      </c>
+      <c r="K17" s="3">
         <v>70500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>66100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>57800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>54900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>53200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>50000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>47600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>44000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>39500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>37000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>34000</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X17" s="3">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y17" s="3">
         <v>28500</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1470,77 +1497,80 @@
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E18" s="3">
         <v>14800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>20400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>16500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>28000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>14100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>10200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>6600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>22200</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3">
         <v>5900</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1550,8 +1580,11 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,77 +1613,78 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4900</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>1600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>5700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-500</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1660,77 +1694,80 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E21" s="3">
         <v>23000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>27600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>27500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>13800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>17100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>13400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>40800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>20600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>15000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>11400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>25900</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3">
         <v>18500</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1740,8 +1777,11 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1769,8 +1809,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1820,168 +1860,177 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E23" s="3">
         <v>18400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>23000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>16800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>9700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>33700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>14300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>9900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>21700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>7900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E24" s="3">
         <v>4500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-3400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>800</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>1900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-500</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,77 +2109,80 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E26" s="3">
         <v>13900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>18700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>12800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>28200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>13500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>9900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>18800</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X26" s="3">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y26" s="3">
         <v>4100</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2140,77 +2192,80 @@
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E27" s="3">
         <v>13900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>18700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>12800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>28200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>13500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>9900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5400</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X27" s="3">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y27" s="3">
         <v>400</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2220,8 +2275,11 @@
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2441,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,77 +2607,80 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>2000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4900</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-1600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>500</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2620,77 +2690,80 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E33" s="3">
         <v>13900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>18700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>12800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>28200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>13500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>9900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5400</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X33" s="3">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y33" s="3">
         <v>400</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2700,8 +2773,11 @@
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,77 +2856,80 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E35" s="3">
         <v>13900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>18700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>12800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>28200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>13500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>9900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5400</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X35" s="3">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y35" s="3">
         <v>400</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2860,93 +2939,99 @@
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,68 +3091,69 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>101800</v>
+      </c>
+      <c r="E41" s="3">
         <v>100500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>78900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>73500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>80200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>78500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>97700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>105500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>79300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>92400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>52200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>51900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>74500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>82500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>89400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>90600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>76600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>81200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>40600</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3085,68 +3172,71 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E42" s="3">
         <v>40100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>61500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>92100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>93900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>96800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>73600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>65400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>93900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>82000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>113900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>131100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>100300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>77100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>47400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>31400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>33400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>19800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>14600</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3165,68 +3255,71 @@
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>349100</v>
+      </c>
+      <c r="E43" s="3">
         <v>424800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>376800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>351600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>303300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>375500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>291400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>258000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>253000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>314300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>277300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>264000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>218400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>286900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>228400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>195400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>173100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>219500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>140500</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3245,8 +3338,11 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3274,8 +3370,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3325,8 +3421,11 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3354,39 +3453,39 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>14800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>14200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>13000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>14200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>8000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7500</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3405,68 +3504,71 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>505300</v>
+      </c>
+      <c r="E46" s="3">
         <v>575500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>529800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>532000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>488900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>562000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>474400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>443200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>440300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>503500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>458200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>460100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>404900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>460700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>378100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>331600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>291100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>327100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>203200</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3485,8 +3587,11 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3514,8 +3619,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3565,68 +3670,71 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E48" s="3">
         <v>102900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>97700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>82100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>80000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>81800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>83700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>89000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>93400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>97400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>102700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>91600</v>
-      </c>
-      <c r="O48" s="3">
-        <v>71800</v>
       </c>
       <c r="P48" s="3">
         <v>71800</v>
       </c>
       <c r="Q48" s="3">
+        <v>71800</v>
+      </c>
+      <c r="R48" s="3">
         <v>51900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>43600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>34000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>30000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>27500</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3645,43 +3753,46 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E49" s="3">
         <v>33900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>34300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>34700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>35000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>35400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>35800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>36200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>36600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>37900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>38700</v>
-      </c>
-      <c r="N49" s="3">
-        <v>6300</v>
       </c>
       <c r="O49" s="3">
         <v>6300</v>
@@ -3704,8 +3815,8 @@
       <c r="U49" s="3">
         <v>6300</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
+      <c r="V49" s="3">
+        <v>6300</v>
       </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
@@ -3725,8 +3836,11 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,68 +4002,71 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E52" s="3">
         <v>2300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>14700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3100</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3965,8 +4085,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,68 +4168,71 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>668600</v>
+      </c>
+      <c r="E54" s="3">
         <v>739500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>689100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>673100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>626200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>695200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>613000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>583700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>577500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>642200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>602200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>570200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>497600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>550200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>438800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>383800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>333500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>371200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>240100</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4125,8 +4251,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,68 +4315,69 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>323600</v>
+      </c>
+      <c r="E57" s="3">
         <v>386600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>360700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>340800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>289200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>347700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>273200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>240100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>222600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>266500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>238400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>19000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>177000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>235400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>185500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>151600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>127200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>176700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>118500</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4265,38 +4396,41 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E58" s="3">
         <v>6000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5800</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4345,8 +4479,11 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4374,39 +4511,39 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>35500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>40600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>236500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>23500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>31500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>27500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>24800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>18100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>14800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11000</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4425,68 +4562,71 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>350200</v>
+      </c>
+      <c r="E60" s="3">
         <v>418800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>392800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>370100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>315800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>379600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>303900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>268800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>247600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>302000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>279000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>255400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>200600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>267000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>213000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>176400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>145300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>191600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>129600</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4505,38 +4645,41 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E61" s="3">
         <v>39900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>29500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>16700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>18100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>16100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>17400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>18800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>20400</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4585,68 +4728,71 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E62" s="3">
         <v>3600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3700</v>
-      </c>
-      <c r="F62" s="3">
-        <v>3600</v>
       </c>
       <c r="G62" s="3">
         <v>3600</v>
       </c>
       <c r="H62" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I62" s="3">
         <v>3400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>28000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>30600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>30900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>29300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>26100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2400</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4665,8 +4811,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,68 +5060,71 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>393000</v>
+      </c>
+      <c r="E66" s="3">
         <v>462300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>425900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>390400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>337500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>399000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>324400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>289100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>271100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>330000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>309600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>286300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>229900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>293000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>218000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>181700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>149400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>195800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>132000</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4985,8 +5143,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5232,11 +5400,11 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>61200</v>
       </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
       <c r="W70" s="3">
         <v>0</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,68 +5506,71 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>139900</v>
+      </c>
+      <c r="E72" s="3">
         <v>149400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>135500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>136400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>134400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>136900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>118200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>116400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>122100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>128000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>115200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>111900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>104100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>99300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>71100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>57500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>47600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>42700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>23900</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5415,8 +5589,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,68 +5838,71 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>275600</v>
+      </c>
+      <c r="E76" s="3">
         <v>277300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>263200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>282700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>288700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>296200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>288600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>294500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>306400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>312200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>292600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>283900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>267700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>257200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>220800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>202100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>184100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>175400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>46900</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5735,8 +5921,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,162 +6004,168 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E81" s="3">
         <v>13900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>18700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>12800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>28200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>13500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>9900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5400</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X81" s="3">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y81" s="3">
         <v>400</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5980,8 +6175,11 @@
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,65 +6208,66 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E83" s="3">
         <v>6600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>8600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>10700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>9100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>6300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4200</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6090,8 +6289,11 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,65 +6704,68 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E89" s="3">
         <v>18000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>19100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>24300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>28700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>23800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>15800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>12800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>19400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>28100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>20500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>19300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>28500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>26400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>21100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>12700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>8600</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6570,8 +6787,11 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,65 +6820,66 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-17400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-14800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11300</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6680,8 +6901,11 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,65 +7067,68 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E94" s="3">
         <v>12700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>15500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-31300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>24400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-18300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>20200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-28000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-45800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-27800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-39600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-28900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-11300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-16800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-18100</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6920,8 +7150,11 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7183,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6979,8 +7213,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7030,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,65 +7513,68 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-29300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-16600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-18700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-16600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-17800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-14000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>48100</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7350,8 +7596,11 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7379,8 +7628,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7430,65 +7679,68 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E102" s="3">
         <v>21500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-19200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-7800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>26300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-13100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>40200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-22600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-8000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>14000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>40600</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7508,6 +7760,9 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PUBM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PUBM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="92">
   <si>
     <t>PUBM</t>
   </si>
@@ -656,378 +656,391 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>71100</v>
+      </c>
+      <c r="E8" s="3">
         <v>63800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>85500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>71800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>67300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>66700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>84600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>63700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>63300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>55400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>74300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>64500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>63000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>54600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>75600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>58100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>49700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>43600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>56200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>37800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>26400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>28300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>34400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>28500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>27400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>23600</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E9" s="3">
         <v>25600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>24900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>25500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>25200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>25400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>24200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>26100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>25100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>23900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>23000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>21600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>19000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>18000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>16900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>16000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>13100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>11500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>10500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>10100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>9300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>9600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8800</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>44500</v>
+      </c>
+      <c r="E10" s="3">
         <v>38200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>60600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>46300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>42100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>41300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>60400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>37600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>38300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>31500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>51300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>42900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>44000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>36600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>58700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>42100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>36600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>31300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>44800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>27300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>17200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>18200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>25100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>18900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>19000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>14800</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,91 +1070,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E12" s="3">
         <v>8800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>8700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>8000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5900</v>
-      </c>
-      <c r="N12" s="3">
-        <v>5100</v>
       </c>
       <c r="O12" s="3">
         <v>5100</v>
       </c>
       <c r="P12" s="3">
+        <v>5100</v>
+      </c>
+      <c r="Q12" s="3">
         <v>4800</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>4100</v>
       </c>
       <c r="R12" s="3">
         <v>4100</v>
       </c>
       <c r="S12" s="3">
+        <v>4100</v>
+      </c>
+      <c r="T12" s="3">
         <v>3900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>3100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>3300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>3100</v>
       </c>
-      <c r="AC12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,8 +1240,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1255,8 +1275,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1306,41 +1326,44 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E15" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F15" s="3">
         <v>6200</v>
       </c>
-      <c r="E15" s="3">
-        <v>6200</v>
-      </c>
-      <c r="F15" s="3">
-        <v>6500</v>
-      </c>
       <c r="G15" s="3">
-        <v>6700</v>
+        <v>7300</v>
       </c>
       <c r="H15" s="3">
+        <v>6300</v>
+      </c>
+      <c r="I15" s="3">
+        <v>6600</v>
+      </c>
+      <c r="J15" s="3">
         <v>7000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>7000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>7600</v>
       </c>
       <c r="K15" s="3">
         <v>7600</v>
       </c>
       <c r="L15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="M15" s="3">
         <v>8600</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,80 +1443,81 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>76600</v>
+      </c>
+      <c r="E17" s="3">
         <v>75700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>70700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>73200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>71300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>72200</v>
-      </c>
-      <c r="I17" s="3">
-        <v>64200</v>
       </c>
       <c r="J17" s="3">
         <v>64200</v>
       </c>
       <c r="K17" s="3">
+        <v>64200</v>
+      </c>
+      <c r="L17" s="3">
         <v>70500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>66100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>57800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>54900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>53200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>50000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>47600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>44000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>39500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>37000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>34000</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z17" s="3">
         <v>28500</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1500,80 +1527,83 @@
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-11900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>14800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>20400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>16500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>28000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>14100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>10200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>6600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>22200</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="3">
         <v>5900</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1583,8 +1613,11 @@
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,80 +1647,81 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4900</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>1600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-500</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1697,80 +1731,83 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-6700</v>
+        <v>-1700</v>
       </c>
       <c r="E21" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="F21" s="3">
         <v>23000</v>
       </c>
-      <c r="F21" s="3">
-        <v>4200</v>
-      </c>
       <c r="G21" s="3">
-        <v>6800</v>
+        <v>5000</v>
       </c>
       <c r="H21" s="3">
-        <v>1700</v>
+        <v>6400</v>
       </c>
       <c r="I21" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J21" s="3">
         <v>27600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>7200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>27500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>13800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>17100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>13400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>40800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>20600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>15000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>11400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>25900</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3">
         <v>18500</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1780,8 +1817,11 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1812,8 +1852,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1863,174 +1903,183 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-11300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>18400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>23000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>16800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>9700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>33700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>14300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>9900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>21700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>7900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>5800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-3400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>800</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>1900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-500</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,80 +2161,83 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>13900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>18700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>12800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>28200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>13500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>9900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>18800</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z26" s="3">
         <v>4100</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2195,80 +2247,83 @@
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>13900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>18700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>12800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>28200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>13500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>9900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5400</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z27" s="3">
         <v>400</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2278,8 +2333,11 @@
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,80 +2677,83 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4900</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>500</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z32" s="3">
         <v>100</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2693,80 +2763,83 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>13900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>18700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>12800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>28200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>13500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>9900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5400</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z33" s="3">
         <v>400</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2776,8 +2849,11 @@
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,80 +2935,83 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>13900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>18700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>12800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>28200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>13500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>9900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5400</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z35" s="3">
         <v>400</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2942,96 +3021,102 @@
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,71 +3178,72 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>90500</v>
+      </c>
+      <c r="E41" s="3">
         <v>101800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>100500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>78900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>73500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>80200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>78500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>97700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>105500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>79300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>92400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>52200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>51900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>74500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>82500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>89400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>90600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>76600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>81200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>40600</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3175,71 +3262,74 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E42" s="3">
         <v>42300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>40100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>61500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>92100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>93900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>96800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>73600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>65400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>93900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>82000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>113900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>131100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>100300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>77100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>47400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>31400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>33400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>19800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>14600</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3258,71 +3348,74 @@
       <c r="AC42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>383400</v>
+      </c>
+      <c r="E43" s="3">
         <v>349100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>424800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>376800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>351600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>303300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>375500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>291400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>258000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>253000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>314300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>277300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>264000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>218400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>286900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>228400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>195400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>173100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>219500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>140500</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3341,8 +3434,11 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3373,8 +3469,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3424,8 +3520,11 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3456,39 +3555,39 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>14800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>13100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>11800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>14200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>13000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>14200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>8000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7500</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3507,71 +3606,74 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>513000</v>
+      </c>
+      <c r="E46" s="3">
         <v>505300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>575500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>529800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>532000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>488900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>562000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>474400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>443200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>440300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>503500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>458200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>460100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>404900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>460700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>378100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>331600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>291100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>327100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>203200</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3590,8 +3692,11 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3622,8 +3727,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3673,71 +3778,74 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>93500</v>
+      </c>
+      <c r="E48" s="3">
         <v>97000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>102900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>97700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>82100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>80000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>81800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>83700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>89000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>93400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>97400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>102700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>91600</v>
-      </c>
-      <c r="P48" s="3">
-        <v>71800</v>
       </c>
       <c r="Q48" s="3">
         <v>71800</v>
       </c>
       <c r="R48" s="3">
+        <v>71800</v>
+      </c>
+      <c r="S48" s="3">
         <v>51900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>43600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>34000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>30000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>27500</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3756,46 +3864,49 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E49" s="3">
         <v>33500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>33900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>34300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>34700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>35000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>35400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>35800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>36200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>36600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>37900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>38700</v>
-      </c>
-      <c r="O49" s="3">
-        <v>6300</v>
       </c>
       <c r="P49" s="3">
         <v>6300</v>
@@ -3818,8 +3929,8 @@
       <c r="V49" s="3">
         <v>6300</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
+      <c r="W49" s="3">
+        <v>6300</v>
       </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
@@ -3839,8 +3950,11 @@
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,71 +4122,74 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E52" s="3">
         <v>3300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>12300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>14700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>11500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3100</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4088,8 +4208,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,71 +4294,74 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>675200</v>
+      </c>
+      <c r="E54" s="3">
         <v>668600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>739500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>689100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>673100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>626200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>695200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>613000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>583700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>577500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>642200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>602200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>570200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>497600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>550200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>438800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>383800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>333500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>371200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>240100</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4254,8 +4380,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,71 +4446,72 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>361400</v>
+      </c>
+      <c r="E57" s="3">
         <v>323600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>386600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>360700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>340800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>289200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>347700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>273200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>240100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>222600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>266500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>238400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>19000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>177000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>235400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>185500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>151600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>127200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>176700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>118500</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4399,41 +4530,44 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E58" s="3">
         <v>6400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5800</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4482,8 +4616,11 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4514,39 +4651,39 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>35500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>40600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>236500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>23500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>31500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>27500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>24800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>18100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>14800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>11000</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4565,71 +4702,74 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>388700</v>
+      </c>
+      <c r="E60" s="3">
         <v>350200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>418800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>392800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>370100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>315800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>379600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>303900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>268800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>247600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>302000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>279000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>255400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>200600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>267000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>213000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>176400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>145300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>191600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>129600</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4648,41 +4788,44 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>39200</v>
+      </c>
+      <c r="E61" s="3">
         <v>39000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>39900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>29500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>16700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>18100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>16100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>17400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>18800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>20400</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -4731,71 +4874,74 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3700</v>
-      </c>
-      <c r="G62" s="3">
-        <v>3600</v>
       </c>
       <c r="H62" s="3">
         <v>3600</v>
       </c>
       <c r="I62" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J62" s="3">
         <v>3400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>28000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>30600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>30900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>29300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>26100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2400</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4814,8 +4960,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,71 +5218,74 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>431900</v>
+      </c>
+      <c r="E66" s="3">
         <v>393000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>462300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>425900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>390400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>337500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>399000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>324400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>289100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>271100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>330000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>309600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>286300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>229900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>293000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>218000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>181700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>149400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>195800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>132000</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5146,8 +5304,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5403,11 +5571,11 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>61200</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,71 +5680,74 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>134700</v>
+      </c>
+      <c r="E72" s="3">
         <v>139900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>149400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>135500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>136400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>134400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>136900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>118200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>116400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>122100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>128000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>115200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>111900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>104100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>99300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>71100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>57500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>47600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>42700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>23900</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5592,8 +5766,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,71 +6024,74 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>243300</v>
+      </c>
+      <c r="E76" s="3">
         <v>275600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>277300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>263200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>282700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>288700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>296200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>288600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>294500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>306400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>312200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>292600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>283900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>267700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>257200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>220800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>202100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>184100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>175400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>46900</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5924,8 +6110,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,168 +6196,174 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>13900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>18700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>12800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>28200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>13500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>9900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5400</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z81" s="3">
         <v>400</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6178,8 +6373,11 @@
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,68 +6407,69 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>7000</v>
+        <v>6300</v>
       </c>
       <c r="E83" s="3">
         <v>6600</v>
       </c>
       <c r="F83" s="3">
+        <v>6600</v>
+      </c>
+      <c r="G83" s="3">
         <v>7200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>8600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>10700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>9100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>6300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4200</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6292,8 +6491,11 @@
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,68 +6921,71 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E89" s="3">
         <v>15600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>18000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>19100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>11900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>24300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>28700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>23800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>15800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>12800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>19400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>28100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>20500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>19300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>28500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>26400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>21100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>12700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>8600</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6790,8 +7007,11 @@
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,68 +7041,69 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-12300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-17400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-14800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-9800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-11300</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6904,8 +7125,11 @@
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,68 +7297,71 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>12700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>15500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-31300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>24400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-18300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>20200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-28000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-45800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-27800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-39600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-28900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-11300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-16800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-18100</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7153,8 +7383,11 @@
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7216,8 +7450,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,68 +7759,71 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-36700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-8900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-29300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-16600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-18700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-16600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-17800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-14000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-7600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>4300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>48100</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7599,8 +7845,11 @@
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7631,8 +7880,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -7682,68 +7931,71 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E102" s="3">
         <v>1400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>21500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-19200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>26300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>40200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-22600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>14000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>40600</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7763,6 +8015,9 @@
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PUBM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PUBM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="92">
   <si>
     <t>PUBM</t>
   </si>
@@ -656,404 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E8" s="3">
         <v>68000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>71100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>63800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>85500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>71800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>67300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>66700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>84600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>63700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>63300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>55400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>74300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>64500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>63000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>54600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>75600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>58100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>49700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>43600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>56200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>37800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>26400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>28300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>34400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>28500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>27400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>23600</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E9" s="3">
         <v>25400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>26600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>25600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>24900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>25500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>25200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>25400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>24200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>26100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>25100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>23900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>23000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>21600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>19000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>18000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>16900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>16000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>13100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>12300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>11500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>10500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>9200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>10100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>9300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>9600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8800</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>54600</v>
+      </c>
+      <c r="E10" s="3">
         <v>42600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>44500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>38200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>60600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>46300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>42100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>41300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>60400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>37600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>38300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>31500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>51300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>42900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>44000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>36600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>58700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>42100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>36600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>31300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>44800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>27300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>17200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>18200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>25100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>18900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>19000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>14800</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1085,97 +1097,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E12" s="3">
         <v>9600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>9100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>8800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>8700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>8000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5900</v>
-      </c>
-      <c r="P12" s="3">
-        <v>5100</v>
       </c>
       <c r="Q12" s="3">
         <v>5100</v>
       </c>
       <c r="R12" s="3">
+        <v>5100</v>
+      </c>
+      <c r="S12" s="3">
         <v>4800</v>
-      </c>
-      <c r="S12" s="3">
-        <v>4100</v>
       </c>
       <c r="T12" s="3">
         <v>4100</v>
       </c>
       <c r="U12" s="3">
+        <v>4100</v>
+      </c>
+      <c r="V12" s="3">
         <v>3900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>3400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>3000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>2900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>3100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>3000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>3300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>3100</v>
       </c>
-      <c r="AE12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1263,13 +1279,16 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>900</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1301,8 +1320,8 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1352,47 +1371,50 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E15" s="3">
         <v>5400</v>
-      </c>
-      <c r="E15" s="3">
-        <v>5800</v>
       </c>
       <c r="F15" s="3">
         <v>5800</v>
       </c>
       <c r="G15" s="3">
+        <v>5800</v>
+      </c>
+      <c r="H15" s="3">
         <v>6200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>6600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>7000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>7600</v>
       </c>
       <c r="M15" s="3">
         <v>7600</v>
       </c>
       <c r="N15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="O15" s="3">
         <v>8600</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1441,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,86 +1496,87 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>70600</v>
+      </c>
+      <c r="E17" s="3">
         <v>76400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>76600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>75700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>70700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>73200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>71300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>72200</v>
-      </c>
-      <c r="K17" s="3">
-        <v>64200</v>
       </c>
       <c r="L17" s="3">
         <v>64200</v>
       </c>
       <c r="M17" s="3">
+        <v>64200</v>
+      </c>
+      <c r="N17" s="3">
         <v>70500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>66100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>57800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>54900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>53200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>50000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>47600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>44000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>39500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>37000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>34000</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB17" s="3">
         <v>28500</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1560,86 +1586,89 @@
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-8400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-5500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-11900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>14800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>20400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-10700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>16500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>9600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>9800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>28000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>14100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>10200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>6600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>22200</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB18" s="3">
         <v>5900</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1649,8 +1678,11 @@
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1682,86 +1714,87 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3">
         <v>900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>1600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>5700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-500</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-100</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1771,86 +1804,89 @@
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-4000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-7100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>23000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>27600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>27500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>13800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>17100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>13400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>40800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>20600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>15000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>11400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>25900</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB21" s="3">
         <v>18500</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1860,8 +1896,11 @@
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1898,8 +1937,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1949,186 +1988,195 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-11300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>18400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>23000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>16800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>9700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>33700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>14300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>9900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>21700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>7900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>5800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-3400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>800</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>1900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-500</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,86 +2264,89 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>13900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>18700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>12800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>28200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>13500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>9900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>18800</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB26" s="3">
         <v>4100</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2305,86 +2356,89 @@
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>13900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>18700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>12800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>7800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>28200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>13500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>9900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5400</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB27" s="3">
         <v>400</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2394,8 +2448,11 @@
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2572,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,86 +2816,89 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4900</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-1600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-5700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>500</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB32" s="3">
         <v>100</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2839,86 +2908,89 @@
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>13900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>18700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>12800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>28200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>13500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>9900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5400</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB33" s="3">
         <v>400</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2928,8 +3000,11 @@
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,86 +3092,89 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>13900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>18700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>12800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>28200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>13500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>9900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5400</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB35" s="3">
         <v>400</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3106,102 +3184,108 @@
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,77 +3351,78 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>145500</v>
+      </c>
+      <c r="E41" s="3">
         <v>136500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>90500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>101800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>100500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>78900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>73500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>80200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>78500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>97700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>105500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>79300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>92400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>52200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>51900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>74500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>82500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>89400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>90600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>76600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>81200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>40600</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3355,8 +3441,11 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3364,68 +3453,68 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>27100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>42300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>40100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>61500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>92100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>93900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>96800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>73600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>65400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>93900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>82000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>113900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>131100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>100300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>77100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>47400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>31400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>33400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>19800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>14600</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3444,77 +3533,80 @@
       <c r="AE42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>358200</v>
+      </c>
+      <c r="E43" s="3">
         <v>362600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>383400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>349100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>424800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>376800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>351600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>303300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>375500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>291400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>258000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>253000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>314300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>277300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>264000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>218400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>286900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>228400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>195400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>173100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>219500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>140500</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3533,8 +3625,11 @@
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3571,8 +3666,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3622,8 +3717,11 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3660,39 +3758,39 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>14800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>14900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>13100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>11800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>14200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>13000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>14200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7500</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3711,77 +3809,80 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>522600</v>
+      </c>
+      <c r="E46" s="3">
         <v>520400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>513000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>505300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>575500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>529800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>532000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>488900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>562000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>474400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>443200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>440300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>503500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>458200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>460100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>404900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>460700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>378100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>331600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>291100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>327100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>203200</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3800,8 +3901,11 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3838,8 +3942,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3889,77 +3993,80 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>90800</v>
+      </c>
+      <c r="E48" s="3">
         <v>91400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>93500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>97000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>102900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>97700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>82100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>80000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>81800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>83700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>89000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>93400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>97400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>102700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>91600</v>
-      </c>
-      <c r="R48" s="3">
-        <v>71800</v>
       </c>
       <c r="S48" s="3">
         <v>71800</v>
       </c>
       <c r="T48" s="3">
+        <v>71800</v>
+      </c>
+      <c r="U48" s="3">
         <v>51900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>43600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>34000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>30000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>27500</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3978,52 +4085,55 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E49" s="3">
         <v>32700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>33100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>33500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>33900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>34300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>34700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>35000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>35400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>35800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>36200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>36600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>37900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>38700</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>6300</v>
       </c>
       <c r="R49" s="3">
         <v>6300</v>
@@ -4046,8 +4156,8 @@
       <c r="X49" s="3">
         <v>6300</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
+      <c r="Y49" s="3">
+        <v>6300</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>3</v>
@@ -4067,8 +4177,11 @@
       <c r="AE49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,77 +4361,80 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E52" s="3">
         <v>3400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>12300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>14700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3100</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4334,8 +4453,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,77 +4545,80 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>680200</v>
+      </c>
+      <c r="E54" s="3">
         <v>676200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>675200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>668600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>739500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>689100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>673100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>626200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>695200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>613000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>583700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>577500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>642200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>602200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>570200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>497600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>550200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>438800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>383800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>333500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>371200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>240100</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4512,8 +4637,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,77 +4707,78 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>343600</v>
+      </c>
+      <c r="E57" s="3">
         <v>356500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>361400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>323600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>386600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>360700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>340800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>289200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>347700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>273200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>240100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>222600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>266500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>238400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>19000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>177000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>235400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>185500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>151600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>127200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>176700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>118500</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4667,47 +4797,50 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E58" s="3">
         <v>6400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5800</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -4756,8 +4889,11 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4794,39 +4930,39 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3">
         <v>35500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>40600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>236500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>23500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>31500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>27500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>24800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>18100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>14800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>11000</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4845,77 +4981,80 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>375900</v>
+      </c>
+      <c r="E60" s="3">
         <v>388400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>388700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>350200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>418800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>392800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>370100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>315800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>379600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>303900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>268800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>247600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>302000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>279000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>255400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>200600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>267000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>213000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>176400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>145300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>191600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>129600</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4934,47 +5073,50 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>37100</v>
+      </c>
+      <c r="E61" s="3">
         <v>38600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>39200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>39000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>39900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>29500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>16700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>18100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>16100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>17400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>18800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>20400</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -5023,77 +5165,80 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E62" s="3">
         <v>4100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3700</v>
-      </c>
-      <c r="I62" s="3">
-        <v>3600</v>
       </c>
       <c r="J62" s="3">
         <v>3600</v>
       </c>
       <c r="K62" s="3">
+        <v>3600</v>
+      </c>
+      <c r="L62" s="3">
         <v>3400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>28000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>30600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>30900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>29300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>26100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2400</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5112,8 +5257,11 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,77 +5533,80 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>417600</v>
+      </c>
+      <c r="E66" s="3">
         <v>431100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>431900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>393000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>462300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>425900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>390400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>337500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>399000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>324400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>289100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>271100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>330000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>309600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>286300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>229900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>293000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>218000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>181700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>149400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>195800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>132000</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5468,8 +5625,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5745,11 +5912,11 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
         <v>61200</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
       <c r="Z70" s="3">
         <v>0</v>
       </c>
@@ -5768,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,77 +6027,80 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>134900</v>
+      </c>
+      <c r="E72" s="3">
         <v>128200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>134700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>139900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>149400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>135500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>136400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>134400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>136900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>118200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>116400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>122100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>128000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>115200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>111900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>104100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>99300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>71100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>57500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>47600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>42700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>23900</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5946,8 +6119,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,77 +6395,80 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>262600</v>
+      </c>
+      <c r="E76" s="3">
         <v>245100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>243300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>275600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>277300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>263200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>282700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>288700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>296200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>288600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>294500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>306400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>312200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>292600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>283900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>267700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>257200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>220800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>202100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>184100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>175400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>46900</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6302,8 +6487,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,180 +6579,186 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>13900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>18700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>12800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>28200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>13500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>9900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5400</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB81" s="3">
         <v>400</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6574,8 +6768,11 @@
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,74 +6804,75 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E83" s="3">
         <v>6100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6300</v>
-      </c>
-      <c r="F83" s="3">
-        <v>6600</v>
       </c>
       <c r="G83" s="3">
         <v>6600</v>
       </c>
       <c r="H83" s="3">
+        <v>6600</v>
+      </c>
+      <c r="I83" s="3">
         <v>7200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>8600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>10700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>9100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>6300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>5100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4200</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6696,8 +6894,11 @@
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,74 +7354,77 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E89" s="3">
         <v>32400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>14900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>15600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>18000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>19100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>24300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>28700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>23800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>15800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>12800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>19400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>28100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>20500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>19300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>28500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>26400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>21100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>12700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>8600</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7230,8 +7446,11 @@
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,74 +7482,75 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-12300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-17400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-14800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-9800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-13000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-13400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-11300</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7352,8 +7572,11 @@
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,74 +7756,77 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E94" s="3">
         <v>17500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>9900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>12700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>15500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-31300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-13900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>24400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-18300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>20200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-28000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-45800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-27800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-39600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-28900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-11300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-16800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-18100</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7619,8 +7848,11 @@
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7690,8 +7923,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7741,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,74 +8250,77 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-36700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-29300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-16600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-18700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-16600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-17800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-14000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-7600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>4200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>48100</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8097,13 +8342,16 @@
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>-300</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>3</v>
@@ -8135,8 +8383,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -8186,74 +8434,77 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E102" s="3">
         <v>46100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>21500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-19200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>26300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>40200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-22600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-8000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>14000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>40600</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8273,6 +8524,9 @@
         <v>3</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PUBM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PUBM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="92">
   <si>
     <t>PUBM</t>
   </si>
@@ -656,416 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>62600</v>
+      </c>
+      <c r="E8" s="3">
         <v>80000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>68000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>71100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>63800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>85500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>71800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>67300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>66700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>84600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>63700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>63300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>55400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>74300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>64500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>63000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>54600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>75600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>58100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>49700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>43600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>56200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>37800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>26400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>28300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>34400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>28500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>27400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>23600</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E9" s="3">
         <v>25500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>25400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>26600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>25600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>24900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>25500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>25200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>25400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>24200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>26100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>25100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>23900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>23000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>21600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>19000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>18000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>16900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>16000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>13100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>12300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>11500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>10500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>9200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>10100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>9300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>9600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>8800</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>36500</v>
+      </c>
+      <c r="E10" s="3">
         <v>54600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>42600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>44500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>38200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>60600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>46300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>42100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>41300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>60400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>37600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>38300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>31500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>51300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>42900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>44000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>36600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>58700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>42100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>36600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>31300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>44800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>27300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>17200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>18200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>25100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>18900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>19000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>14800</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,100 +1111,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E12" s="3">
         <v>6300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>9600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>9100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>8800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>7800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>8800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>8700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>8000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5900</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>5100</v>
       </c>
       <c r="R12" s="3">
         <v>5100</v>
       </c>
       <c r="S12" s="3">
+        <v>5100</v>
+      </c>
+      <c r="T12" s="3">
         <v>4800</v>
-      </c>
-      <c r="T12" s="3">
-        <v>4100</v>
       </c>
       <c r="U12" s="3">
         <v>4100</v>
       </c>
       <c r="V12" s="3">
+        <v>4100</v>
+      </c>
+      <c r="W12" s="3">
         <v>3900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>3000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>3400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>2900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>3100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>3000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>3300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>3100</v>
       </c>
-      <c r="AF12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,17 +1299,20 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>900</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1323,8 +1343,8 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1374,50 +1394,53 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E15" s="3">
         <v>3700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5400</v>
-      </c>
-      <c r="F15" s="3">
-        <v>5800</v>
       </c>
       <c r="G15" s="3">
         <v>5800</v>
       </c>
       <c r="H15" s="3">
+        <v>5800</v>
+      </c>
+      <c r="I15" s="3">
         <v>6200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>6300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>6600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>7000</v>
-      </c>
-      <c r="M15" s="3">
-        <v>7600</v>
       </c>
       <c r="N15" s="3">
         <v>7600</v>
       </c>
       <c r="O15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="P15" s="3">
         <v>8600</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1466,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,89 +1523,90 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>77800</v>
+      </c>
+      <c r="E17" s="3">
         <v>70600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>76400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>76600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>75700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>70700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>73200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>71300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>72200</v>
-      </c>
-      <c r="L17" s="3">
-        <v>64200</v>
       </c>
       <c r="M17" s="3">
         <v>64200</v>
       </c>
       <c r="N17" s="3">
+        <v>64200</v>
+      </c>
+      <c r="O17" s="3">
         <v>70500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>66100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>57800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>54900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>53200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>50000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>47600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>44000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>39500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>37000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>34000</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC17" s="3">
         <v>28500</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1589,89 +1616,92 @@
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="E18" s="3">
         <v>9400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-8400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-11900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>14800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>20400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-10700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>16500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>9600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>9800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>28000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>14100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>10200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>6600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>22200</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC18" s="3">
         <v>5900</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1681,8 +1711,11 @@
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,89 +1748,90 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4900</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>1600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>5700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-500</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-100</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1807,89 +1841,92 @@
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="E21" s="3">
         <v>12900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-7100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>23000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>27600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>27500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>13800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>17100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>13400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>40800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>20600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>15000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>11400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>25900</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC21" s="3">
         <v>18500</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1899,8 +1936,11 @@
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1940,8 +1980,8 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1991,192 +2031,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="E23" s="3">
         <v>9600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-11300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>18400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>23000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>16800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>9700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>33700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>14300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>9900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>21700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>7900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>5800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E24" s="3">
         <v>2900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-3400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>800</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>1900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-500</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,89 +2316,92 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="E26" s="3">
         <v>6700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>13900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>18700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>12800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>7800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>28200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>13500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>9900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>18800</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC26" s="3">
         <v>4100</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2359,89 +2411,92 @@
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="E27" s="3">
         <v>6700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>13900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>18700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>12800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>7800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>28200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>13500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>9900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5400</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC27" s="3">
         <v>400</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2451,8 +2506,11 @@
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,89 +2886,92 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4900</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-1600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-5700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>500</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC32" s="3">
         <v>100</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2911,89 +2981,92 @@
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="E33" s="3">
         <v>6700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>13900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>18700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>12800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>28200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>13500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>9900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5400</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC33" s="3">
         <v>400</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
@@ -3003,8 +3076,11 @@
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,89 +3171,92 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="E35" s="3">
         <v>6700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>13900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>18700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>12800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>28200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>13500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>9900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5400</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC35" s="3">
         <v>400</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3187,105 +3266,111 @@
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,80 +3438,81 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>144900</v>
+      </c>
+      <c r="E41" s="3">
         <v>145500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>136500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>90500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>101800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>100500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>78900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>73500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>80200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>78500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>97700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>105500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>79300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>92400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>52200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>51900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>74500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>82500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>89400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>90600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>76600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>81200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>40600</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3444,8 +3531,11 @@
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3456,68 +3546,68 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>27100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>42300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>40100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>61500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>92100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>93900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>96800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>73600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>65400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>93900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>82000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>113900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>131100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>100300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>77100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>47400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>31400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>33400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>19800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>14600</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3536,80 +3626,83 @@
       <c r="AF42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>336900</v>
+      </c>
+      <c r="E43" s="3">
         <v>358200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>362600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>383400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>349100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>424800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>376800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>351600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>303300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>375500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>291400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>258000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>253000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>314300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>277300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>264000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>218400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>286900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>228400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>195400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>173100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>219500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>140500</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3628,8 +3721,11 @@
       <c r="AF43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3669,8 +3765,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3720,8 +3816,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3761,39 +3860,39 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>14800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>14900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>13100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>11800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>14200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>13000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>14200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7500</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3812,80 +3911,83 @@
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>504200</v>
+      </c>
+      <c r="E46" s="3">
         <v>522600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>520400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>513000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>505300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>575500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>529800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>532000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>488900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>562000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>474400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>443200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>440300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>503500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>458200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>460100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>404900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>460700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>378100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>331600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>291100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>327100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>203200</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3904,8 +4006,11 @@
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3945,8 +4050,8 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3996,80 +4101,83 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>86400</v>
+      </c>
+      <c r="E48" s="3">
         <v>90800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>91400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>93500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>97000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>102900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>97700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>82100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>80000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>81800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>83700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>89000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>93400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>97400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>102700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>91600</v>
-      </c>
-      <c r="S48" s="3">
-        <v>71800</v>
       </c>
       <c r="T48" s="3">
         <v>71800</v>
       </c>
       <c r="U48" s="3">
+        <v>71800</v>
+      </c>
+      <c r="V48" s="3">
         <v>51900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>43600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>34000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>30000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>27500</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4088,55 +4196,58 @@
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E49" s="3">
         <v>32300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>32700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>33100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>33500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>33900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>34300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>34700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>35000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>35400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>35800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>36200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>36600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>37900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>38700</v>
-      </c>
-      <c r="R49" s="3">
-        <v>6300</v>
       </c>
       <c r="S49" s="3">
         <v>6300</v>
@@ -4159,8 +4270,8 @@
       <c r="Y49" s="3">
         <v>6300</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>3</v>
+      <c r="Z49" s="3">
+        <v>6300</v>
       </c>
       <c r="AA49" s="3" t="s">
         <v>3</v>
@@ -4180,8 +4291,11 @@
       <c r="AF49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,80 +4481,83 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E52" s="3">
         <v>3500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>12300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>14700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>11500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3100</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4456,8 +4576,11 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,80 +4671,83 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>659400</v>
+      </c>
+      <c r="E54" s="3">
         <v>680200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>676200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>675200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>668600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>739500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>689100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>673100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>626200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>695200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>613000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>583700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>577500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>642200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>602200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>570200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>497600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>550200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>438800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>383800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>333500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>371200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>240100</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4640,8 +4766,11 @@
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,80 +4838,81 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>342600</v>
+      </c>
+      <c r="E57" s="3">
         <v>343600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>356500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>361400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>323600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>386600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>360700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>340800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>289200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>347700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>273200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>240100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>222600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>266500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>238400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>19000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>177000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>235400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>185500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>151600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>127200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>176700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>118500</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4800,50 +4931,53 @@
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E58" s="3">
         <v>7100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5800</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -4892,8 +5026,11 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4933,39 +5070,39 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3">
         <v>35500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>40600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>236500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>23500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>31500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>27500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>24800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>18100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>14800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>11000</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4984,80 +5121,83 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>368900</v>
+      </c>
+      <c r="E60" s="3">
         <v>375900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>388400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>388700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>350200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>418800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>392800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>370100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>315800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>379600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>303900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>268800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>247600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>302000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>279000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>255400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>200600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>267000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>213000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>176400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>145300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>191600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>129600</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5076,50 +5216,53 @@
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E61" s="3">
         <v>37100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>38600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>39200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>39000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>39900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>29500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>16700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>18100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>16100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>17400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>18800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>20400</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -5168,80 +5311,83 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E62" s="3">
         <v>4700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3700</v>
-      </c>
-      <c r="J62" s="3">
-        <v>3600</v>
       </c>
       <c r="K62" s="3">
         <v>3600</v>
       </c>
       <c r="L62" s="3">
+        <v>3600</v>
+      </c>
+      <c r="M62" s="3">
         <v>3400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>28000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>30600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>30900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>29300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>26100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2400</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5260,8 +5406,11 @@
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,80 +5691,83 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>408400</v>
+      </c>
+      <c r="E66" s="3">
         <v>417600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>431100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>431900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>393000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>462300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>425900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>390400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>337500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>399000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>324400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>289100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>271100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>330000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>309600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>286300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>229900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>293000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>218000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>181700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>149400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>195800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>132000</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5628,8 +5786,11 @@
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5915,11 +6083,11 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
         <v>61200</v>
       </c>
-      <c r="Z70" s="3">
-        <v>0</v>
-      </c>
       <c r="AA70" s="3">
         <v>0</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,80 +6201,83 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>122400</v>
+      </c>
+      <c r="E72" s="3">
         <v>134900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>128200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>134700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>139900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>149400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>135500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>136400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>134400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>136900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>118200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>116400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>122100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>128000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>115200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>111900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>104100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>99300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>71100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>57500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>47600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>42700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>23900</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6122,8 +6296,11 @@
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,80 +6581,83 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>251000</v>
+      </c>
+      <c r="E76" s="3">
         <v>262600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>245100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>243300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>275600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>277300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>263200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>282700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>288700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>296200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>288600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>294500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>306400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>312200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>292600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>283900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>267700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>257200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>220800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>202100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>184100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>175400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>46900</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6490,8 +6676,11 @@
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,186 +6771,192 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="E81" s="3">
         <v>6700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>13900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>18700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>12800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>28200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>13500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>9900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5400</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC81" s="3">
         <v>400</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6771,8 +6966,11 @@
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7003,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6814,68 +7013,68 @@
         <v>5800</v>
       </c>
       <c r="E83" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F83" s="3">
         <v>6100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6300</v>
-      </c>
-      <c r="G83" s="3">
-        <v>6600</v>
       </c>
       <c r="H83" s="3">
         <v>6600</v>
       </c>
       <c r="I83" s="3">
+        <v>6600</v>
+      </c>
+      <c r="J83" s="3">
         <v>7200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>10700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>9100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>7100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>6300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>5100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4200</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6897,8 +7096,11 @@
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,77 +7571,80 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E89" s="3">
         <v>18200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>32400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>14900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>15600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>18000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>19100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>11900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>24300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>28700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>23800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>15800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>12800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>19400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>28100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>20500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>19300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>28500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>26400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>21100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>12700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>8600</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7449,8 +7666,11 @@
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,77 +7703,78 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-17400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-14800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-9800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-13000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-13400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-11300</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7575,8 +7796,11 @@
       <c r="AF91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,77 +7986,80 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-11300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>17500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>9900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>12700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>15500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-31300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-13900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>24400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-18300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>20200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-28000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-45800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-27800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-39600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-28900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-11300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-16800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-18100</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7851,8 +8081,11 @@
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7926,8 +8160,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,77 +8496,80 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E100" s="3">
         <v>2200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-36700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-8900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-29300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-16600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-18700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-16600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-17800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-14000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-7600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>4200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>48100</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8345,17 +8591,20 @@
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
       </c>
@@ -8386,8 +8635,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8437,77 +8686,80 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E102" s="3">
         <v>9000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>46100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>21500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-6700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-19200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>26300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-13100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>40200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-22600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-8000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-6900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>14000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>40600</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8527,6 +8779,9 @@
         <v>3</v>
       </c>
       <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
